--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 알파 전투 밸런스 데이터 테이블 V3.1.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 알파 전투 밸런스 데이터 테이블 V3.1.xlsx
@@ -3,14 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GA7thFinal_Orora\2_Documents\강현재\밸런스\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65B6FC7A-A379-41F8-A6E6-3D713457947D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834"/>
   </bookViews>
   <sheets>
     <sheet name="수정 내역" sheetId="41" r:id="rId1"/>
@@ -24,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" chartTrackingRefBase="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2664,7 +2658,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2831,20 +2825,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="표준 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="표준 2" xfId="1" builtinId="0"/>
+    <cellStyle name="표준 3" xfId="2" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3126,14 +3121,14 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -3186,14 +3181,14 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -3246,7 +3241,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -3256,7 +3251,7 @@
             <a:t>협회</a:t>
           </a:r>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -3309,14 +3304,14 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -3369,14 +3364,14 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -3429,14 +3424,14 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -3489,14 +3484,14 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -3552,7 +3547,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -3571,7 +3566,7 @@
           </a:r>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2800" b="1"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -3627,7 +3622,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -3664,7 +3659,7 @@
           </a:r>
           <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000" b="1"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -3720,7 +3715,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -3749,7 +3744,7 @@
           </a:r>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -3805,7 +3800,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -3834,7 +3829,7 @@
           </a:r>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800" b="1"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -3890,7 +3885,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -3911,7 +3906,7 @@
             <a:t>FEP005S1BE122</a:t>
           </a:r>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -3967,7 +3962,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -3996,7 +3991,7 @@
           </a:r>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -4049,7 +4044,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -4078,7 +4073,7 @@
           </a:r>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -4131,7 +4126,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -4159,7 +4154,7 @@
             <a:t>BE160</a:t>
           </a:r>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -4212,7 +4207,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -4241,7 +4236,7 @@
           </a:r>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -8450,7 +8445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DEBB537-D2E1-4D20-A494-C05A81D52093}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:Z40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
@@ -8470,7 +8465,6 @@
     <col min="19" max="19" width="15.58203125" style="11" customWidth="1"/>
     <col min="20" max="20" width="22.83203125" style="11" bestFit="1" customWidth="1"/>
     <col min="21" max="62" width="15.58203125" style="11" customWidth="1"/>
-    <col min="63" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.45">
@@ -8662,10 +8656,10 @@
         <v>185</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>320</v>
+        <v>253</v>
       </c>
       <c r="D6" s="45">
         <v>1</v>
@@ -8692,44 +8686,60 @@
         <v>0</v>
       </c>
       <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="36">
-        <v>1</v>
-      </c>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="44">
+      <c r="M6" s="45">
+        <v>0</v>
+      </c>
+      <c r="N6" s="45">
+        <v>0</v>
+      </c>
+      <c r="O6" s="58">
+        <v>1</v>
+      </c>
+      <c r="P6" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="58">
         <f>O6+10%</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="R6" s="44"/>
-      <c r="S6" s="36">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="R6" s="58">
+        <v>0</v>
+      </c>
+      <c r="S6" s="58">
         <f>Q6+10%</f>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="T6" s="44"/>
-      <c r="U6" s="44">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="T6" s="58">
+        <v>0</v>
+      </c>
+      <c r="U6" s="58">
         <f>S6+10%</f>
-        <v>1.3000000000000003</v>
-      </c>
-      <c r="V6" s="44"/>
-      <c r="W6" s="36">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="V6" s="58">
+        <v>0</v>
+      </c>
+      <c r="W6" s="58">
         <f>U6+10%</f>
-        <v>1.4000000000000004</v>
-      </c>
-      <c r="X6" s="44"/>
-      <c r="Y6" s="32"/>
+        <v>1.39999997615814</v>
+      </c>
+      <c r="X6" s="58">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z6" s="48" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A7" s="7"/>
       <c r="B7" s="45" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>320</v>
+        <v>253</v>
       </c>
       <c r="D7" s="45">
         <v>2</v>
@@ -8753,7 +8763,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="45" t="s">
         <v>132</v>
@@ -8761,48 +8771,52 @@
       <c r="M7" s="45">
         <v>0</v>
       </c>
-      <c r="N7" s="45"/>
-      <c r="O7" s="36">
-        <v>1</v>
-      </c>
-      <c r="P7" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="Q7" s="44">
+      <c r="N7" s="45">
+        <v>0</v>
+      </c>
+      <c r="O7" s="58">
+        <v>1</v>
+      </c>
+      <c r="P7" s="58">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="Q7" s="58">
         <f t="shared" ref="Q7:Q37" si="0">O7+10%</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="R7" s="44">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="R7" s="58">
         <f t="shared" ref="R7:X37" si="1">P7+10%</f>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="S7" s="36">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="S7" s="58">
         <f t="shared" ref="S7:S37" si="2">Q7+10%</f>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="T7" s="44">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="T7" s="58">
         <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="U7" s="44">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="U7" s="58">
         <f t="shared" ref="U7:U37" si="3">S7+10%</f>
-        <v>1.3000000000000003</v>
-      </c>
-      <c r="V7" s="44">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="V7" s="58">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="W7" s="36">
+      <c r="W7" s="58">
         <f t="shared" ref="W7:W37" si="4">U7+10%</f>
-        <v>1.4000000000000004</v>
-      </c>
-      <c r="X7" s="44">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="X7" s="58">
         <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
-      <c r="Y7" s="32"/>
+        <v>0.600000023841858</v>
+      </c>
+      <c r="Y7" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z7" s="48" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
@@ -8811,7 +8825,7 @@
         <v>325</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>320</v>
+        <v>253</v>
       </c>
       <c r="D8" s="45">
         <v>3</v>
@@ -8835,7 +8849,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="45" t="s">
         <v>80</v>
@@ -8846,47 +8860,49 @@
       <c r="N8" s="45">
         <v>1</v>
       </c>
-      <c r="O8" s="36">
-        <v>0.6</v>
-      </c>
-      <c r="P8" s="36">
-        <v>0.8</v>
-      </c>
-      <c r="Q8" s="44">
+      <c r="O8" s="58">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="P8" s="58">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="Q8" s="58">
         <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="R8" s="44">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="R8" s="58">
         <f t="shared" si="1"/>
-        <v>0.9</v>
-      </c>
-      <c r="S8" s="36">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="S8" s="58">
         <f t="shared" si="2"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="T8" s="44">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="T8" s="58">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="U8" s="44">
+      <c r="U8" s="58">
         <f t="shared" si="3"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="V8" s="44">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="V8" s="58">
         <f t="shared" si="1"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="W8" s="36">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="W8" s="58">
         <f t="shared" si="4"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="X8" s="44">
+        <v>1</v>
+      </c>
+      <c r="X8" s="58">
         <f t="shared" si="1"/>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="Y8" s="32"/>
+        <v>1.20000004768372</v>
+      </c>
+      <c r="Y8" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z8" s="48" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
@@ -8895,7 +8911,7 @@
         <v>326</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>320</v>
+        <v>253</v>
       </c>
       <c r="D9" s="45">
         <v>4</v>
@@ -8922,44 +8938,60 @@
         <v>2</v>
       </c>
       <c r="L9" s="45"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="45"/>
-      <c r="O9" s="36">
+      <c r="M9" s="45">
+        <v>0</v>
+      </c>
+      <c r="N9" s="45">
+        <v>0</v>
+      </c>
+      <c r="O9" s="58">
         <v>0.5</v>
       </c>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="44">
+      <c r="P9" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="58">
         <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-      <c r="R9" s="44"/>
-      <c r="S9" s="36">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="R9" s="58">
+        <v>0</v>
+      </c>
+      <c r="S9" s="58">
         <f t="shared" si="2"/>
-        <v>0.7</v>
-      </c>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="T9" s="58">
+        <v>0</v>
+      </c>
+      <c r="U9" s="58">
         <f t="shared" si="3"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="V9" s="44"/>
-      <c r="W9" s="36">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="V9" s="58">
+        <v>0</v>
+      </c>
+      <c r="W9" s="58">
         <f t="shared" si="4"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="X9" s="44"/>
-      <c r="Y9" s="32"/>
+        <v>0.899999976158142</v>
+      </c>
+      <c r="X9" s="58">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z9" s="48" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A10" s="7"/>
       <c r="B10" s="45" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>320</v>
+        <v>253</v>
       </c>
       <c r="D10" s="45">
         <v>5</v>
@@ -8986,46 +9018,60 @@
         <v>0</v>
       </c>
       <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="45"/>
-      <c r="O10" s="36">
-        <v>1.2</v>
-      </c>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="44">
+      <c r="M10" s="45">
+        <v>0</v>
+      </c>
+      <c r="N10" s="45">
+        <v>0</v>
+      </c>
+      <c r="O10" s="58">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="P10" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="58">
         <f t="shared" si="0"/>
-        <v>1.3</v>
-      </c>
-      <c r="R10" s="44"/>
-      <c r="S10" s="36">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="R10" s="58">
+        <v>0</v>
+      </c>
+      <c r="S10" s="58">
         <f t="shared" si="2"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="T10" s="58">
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
         <f t="shared" si="3"/>
-        <v>1.5000000000000002</v>
-      </c>
-      <c r="V10" s="44"/>
-      <c r="W10" s="36">
+        <v>1.5</v>
+      </c>
+      <c r="V10" s="58">
+        <v>0</v>
+      </c>
+      <c r="W10" s="58">
         <f t="shared" si="4"/>
-        <v>1.6000000000000003</v>
-      </c>
-      <c r="X10" s="44"/>
+        <v>1.60000002384186</v>
+      </c>
+      <c r="X10" s="58">
+        <v>0</v>
+      </c>
       <c r="Y10" s="32" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Z10" s="48" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A11" s="7"/>
       <c r="B11" s="45" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>320</v>
+        <v>253</v>
       </c>
       <c r="D11" s="45">
         <v>6</v>
@@ -9057,59 +9103,61 @@
       <c r="M11" s="45">
         <v>0</v>
       </c>
-      <c r="N11" s="45"/>
-      <c r="O11" s="36">
-        <v>1.2</v>
-      </c>
-      <c r="P11" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="Q11" s="44">
+      <c r="N11" s="45">
+        <v>0</v>
+      </c>
+      <c r="O11" s="58">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="P11" s="58">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="Q11" s="58">
         <f t="shared" si="0"/>
-        <v>1.3</v>
-      </c>
-      <c r="R11" s="44">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="R11" s="58">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="S11" s="36">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="S11" s="58">
         <f t="shared" si="2"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="T11" s="44">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="T11" s="58">
         <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="U11" s="44">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="U11" s="58">
         <f t="shared" si="3"/>
-        <v>1.5000000000000002</v>
-      </c>
-      <c r="V11" s="44">
+        <v>1.5</v>
+      </c>
+      <c r="V11" s="58">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="W11" s="36">
+      <c r="W11" s="58">
         <f t="shared" si="4"/>
-        <v>1.6000000000000003</v>
-      </c>
-      <c r="X11" s="44">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="X11" s="58">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.600000023841858</v>
       </c>
       <c r="Y11" s="32" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Z11" s="48" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7"/>
       <c r="B12" s="45" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>320</v>
+        <v>253</v>
       </c>
       <c r="D12" s="45">
         <v>7</v>
@@ -9144,58 +9192,58 @@
       <c r="N12" s="45">
         <v>1</v>
       </c>
-      <c r="O12" s="36">
-        <v>0.7</v>
-      </c>
-      <c r="P12" s="36">
-        <v>0.9</v>
-      </c>
-      <c r="Q12" s="44">
+      <c r="O12" s="58">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="P12" s="58">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="Q12" s="58">
         <f t="shared" si="0"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="R12" s="44">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="R12" s="58">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S12" s="36">
+      <c r="S12" s="58">
         <f t="shared" si="2"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="T12" s="44">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="T12" s="58">
         <f t="shared" si="1"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="U12" s="44">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="U12" s="58">
         <f t="shared" si="3"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="V12" s="44">
+        <v>1</v>
+      </c>
+      <c r="V12" s="58">
         <f t="shared" si="1"/>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="W12" s="36">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="W12" s="58">
         <f t="shared" si="4"/>
-        <v>1.0999999999999999</v>
-      </c>
-      <c r="X12" s="44">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="X12" s="58">
         <f t="shared" si="1"/>
-        <v>1.3000000000000003</v>
+        <v>1.29999995231628</v>
       </c>
       <c r="Y12" s="32" t="s">
         <v>325</v>
       </c>
       <c r="Z12" s="48" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A13" s="7"/>
       <c r="B13" s="45" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>320</v>
+        <v>253</v>
       </c>
       <c r="D13" s="45">
         <v>8</v>
@@ -9222,37 +9270,51 @@
         <v>2</v>
       </c>
       <c r="L13" s="45"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="45"/>
-      <c r="O13" s="36">
-        <v>0.6</v>
-      </c>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="44">
+      <c r="M13" s="45">
+        <v>0</v>
+      </c>
+      <c r="N13" s="45">
+        <v>0</v>
+      </c>
+      <c r="O13" s="58">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="P13" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="58">
         <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="R13" s="44"/>
-      <c r="S13" s="36">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="R13" s="58">
+        <v>0</v>
+      </c>
+      <c r="S13" s="58">
         <f t="shared" si="2"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="T13" s="44"/>
-      <c r="U13" s="44">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="T13" s="58">
+        <v>0</v>
+      </c>
+      <c r="U13" s="58">
         <f t="shared" si="3"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="V13" s="44"/>
-      <c r="W13" s="36">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="V13" s="58">
+        <v>0</v>
+      </c>
+      <c r="W13" s="58">
         <f t="shared" si="4"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="X13" s="44"/>
+        <v>1</v>
+      </c>
+      <c r="X13" s="58">
+        <v>0</v>
+      </c>
       <c r="Y13" s="32" t="s">
         <v>326</v>
       </c>
       <c r="Z13" s="48" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
@@ -9261,10 +9323,10 @@
         <v>386</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>399</v>
+        <v>255</v>
       </c>
       <c r="D14" s="45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14" s="45" t="s">
         <v>400</v>
@@ -9288,35 +9350,51 @@
         <v>0</v>
       </c>
       <c r="L14" s="45"/>
-      <c r="M14" s="45"/>
-      <c r="N14" s="45"/>
-      <c r="O14" s="36">
-        <v>1</v>
-      </c>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="44">
+      <c r="M14" s="45">
+        <v>0</v>
+      </c>
+      <c r="N14" s="45">
+        <v>0</v>
+      </c>
+      <c r="O14" s="58">
+        <v>1</v>
+      </c>
+      <c r="P14" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="58">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="R14" s="44"/>
-      <c r="S14" s="36">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="R14" s="58">
+        <v>0</v>
+      </c>
+      <c r="S14" s="58">
         <f t="shared" si="2"/>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="T14" s="44"/>
-      <c r="U14" s="44">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="T14" s="58">
+        <v>0</v>
+      </c>
+      <c r="U14" s="58">
         <f t="shared" si="3"/>
-        <v>1.3000000000000003</v>
-      </c>
-      <c r="V14" s="44"/>
-      <c r="W14" s="36">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="V14" s="58">
+        <v>0</v>
+      </c>
+      <c r="W14" s="58">
         <f t="shared" si="4"/>
-        <v>1.4000000000000004</v>
-      </c>
-      <c r="X14" s="44"/>
-      <c r="Y14" s="32"/>
+        <v>1.39999997615814</v>
+      </c>
+      <c r="X14" s="58">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z14" s="48" t="s">
-        <v>411</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
@@ -9325,10 +9403,10 @@
         <v>387</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>399</v>
+        <v>255</v>
       </c>
       <c r="D15" s="45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="45" t="s">
         <v>402</v>
@@ -9360,47 +9438,49 @@
       <c r="N15" s="45">
         <v>1</v>
       </c>
-      <c r="O15" s="36">
-        <v>0.9</v>
-      </c>
-      <c r="P15" s="36">
-        <v>0.3</v>
-      </c>
-      <c r="Q15" s="44">
+      <c r="O15" s="58">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="P15" s="58">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="Q15" s="58">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="R15" s="44">
+      <c r="R15" s="58">
         <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="S15" s="36">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="S15" s="58">
         <f t="shared" si="2"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="T15" s="44">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="T15" s="58">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="U15" s="44">
+      <c r="U15" s="58">
         <f t="shared" si="3"/>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="V15" s="44">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="V15" s="58">
         <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
-      <c r="W15" s="36">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="W15" s="58">
         <f t="shared" si="4"/>
-        <v>1.3000000000000003</v>
-      </c>
-      <c r="X15" s="44">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="X15" s="58">
         <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="Y15" s="32"/>
+        <v>0.699999988079071</v>
+      </c>
+      <c r="Y15" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z15" s="48" t="s">
-        <v>412</v>
+        <v>364</v>
       </c>
     </row>
     <row r="16" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
@@ -9409,10 +9489,10 @@
         <v>388</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>399</v>
+        <v>255</v>
       </c>
       <c r="D16" s="45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="45" t="s">
         <v>404</v>
@@ -9441,46 +9521,60 @@
       <c r="M16" s="45">
         <v>0</v>
       </c>
-      <c r="N16" s="45"/>
-      <c r="O16" s="36">
-        <v>0.6</v>
-      </c>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="44">
+      <c r="N16" s="45">
+        <v>0</v>
+      </c>
+      <c r="O16" s="58">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="P16" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="58">
         <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="R16" s="44"/>
-      <c r="S16" s="36">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="R16" s="58">
+        <v>0</v>
+      </c>
+      <c r="S16" s="58">
         <f t="shared" si="2"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="T16" s="44"/>
-      <c r="U16" s="44">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="T16" s="58">
+        <v>0</v>
+      </c>
+      <c r="U16" s="58">
         <f t="shared" si="3"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="V16" s="44"/>
-      <c r="W16" s="36">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="V16" s="58">
+        <v>0</v>
+      </c>
+      <c r="W16" s="58">
         <f t="shared" si="4"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="X16" s="44"/>
-      <c r="Y16" s="32"/>
+        <v>1</v>
+      </c>
+      <c r="X16" s="58">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z16" s="48" t="s">
-        <v>413</v>
+        <v>358</v>
       </c>
     </row>
     <row r="17" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A17" s="7"/>
       <c r="B17" s="45" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>399</v>
+        <v>255</v>
       </c>
       <c r="D17" s="45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="45" t="s">
         <v>406</v>
@@ -9504,58 +9598,64 @@
         <v>2</v>
       </c>
       <c r="L17" s="45"/>
-      <c r="M17" s="45"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="36">
-        <v>0.6</v>
-      </c>
-      <c r="P17" s="36">
-        <v>0.05</v>
-      </c>
-      <c r="Q17" s="44">
+      <c r="M17" s="45">
+        <v>0</v>
+      </c>
+      <c r="N17" s="45">
+        <v>0</v>
+      </c>
+      <c r="O17" s="58">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="P17" s="58">
+        <v>0.0500000007450581</v>
+      </c>
+      <c r="Q17" s="58">
         <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="R17" s="44">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="R17" s="58">
         <f t="shared" si="1"/>
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="S17" s="36">
+        <v>0.150000005960464</v>
+      </c>
+      <c r="S17" s="58">
         <f t="shared" si="2"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="T17" s="44">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="T17" s="58">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
-      <c r="U17" s="44">
+      <c r="U17" s="58">
         <f t="shared" si="3"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="V17" s="44">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="V17" s="58">
         <f t="shared" si="1"/>
-        <v>0.35</v>
-      </c>
-      <c r="W17" s="36">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="W17" s="58">
         <f t="shared" si="4"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="X17" s="44">
+        <v>1</v>
+      </c>
+      <c r="X17" s="58">
         <f t="shared" si="1"/>
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="Y17" s="32"/>
+        <v>0.449999988079071</v>
+      </c>
+      <c r="Y17" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z17" s="48" t="s">
-        <v>413</v>
+        <v>358</v>
       </c>
     </row>
     <row r="18" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A18" s="7"/>
       <c r="B18" s="45" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>399</v>
+        <v>255</v>
       </c>
       <c r="D18" s="45">
         <v>5</v>
@@ -9582,46 +9682,60 @@
         <v>0</v>
       </c>
       <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="36">
-        <v>1.2</v>
-      </c>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="44">
+      <c r="M18" s="45">
+        <v>0</v>
+      </c>
+      <c r="N18" s="45">
+        <v>0</v>
+      </c>
+      <c r="O18" s="58">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="P18" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="58">
         <f t="shared" si="0"/>
-        <v>1.3</v>
-      </c>
-      <c r="R18" s="44"/>
-      <c r="S18" s="36">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="R18" s="58">
+        <v>0</v>
+      </c>
+      <c r="S18" s="58">
         <f t="shared" si="2"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="T18" s="44"/>
-      <c r="U18" s="44">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="T18" s="58">
+        <v>0</v>
+      </c>
+      <c r="U18" s="58">
         <f t="shared" si="3"/>
-        <v>1.5000000000000002</v>
-      </c>
-      <c r="V18" s="44"/>
-      <c r="W18" s="36">
+        <v>1.5</v>
+      </c>
+      <c r="V18" s="58">
+        <v>0</v>
+      </c>
+      <c r="W18" s="58">
         <f t="shared" si="4"/>
-        <v>1.6000000000000003</v>
-      </c>
-      <c r="X18" s="44"/>
+        <v>1.60000002384186</v>
+      </c>
+      <c r="X18" s="58">
+        <v>0</v>
+      </c>
       <c r="Y18" s="32" t="s">
         <v>386</v>
       </c>
       <c r="Z18" s="48" t="s">
-        <v>411</v>
+        <v>361</v>
       </c>
     </row>
     <row r="19" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7"/>
       <c r="B19" s="45" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>399</v>
+        <v>255</v>
       </c>
       <c r="D19" s="45">
         <v>6</v>
@@ -9656,58 +9770,58 @@
       <c r="N19" s="45">
         <v>1</v>
       </c>
-      <c r="O19" s="36">
-        <v>1</v>
-      </c>
-      <c r="P19" s="36">
-        <v>0.4</v>
-      </c>
-      <c r="Q19" s="44">
+      <c r="O19" s="58">
+        <v>1</v>
+      </c>
+      <c r="P19" s="58">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="Q19" s="58">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="R19" s="44">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="R19" s="58">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="S19" s="36">
+      <c r="S19" s="58">
         <f t="shared" si="2"/>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="T19" s="44">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="T19" s="58">
         <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
-      <c r="U19" s="44">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="U19" s="58">
         <f t="shared" si="3"/>
-        <v>1.3000000000000003</v>
-      </c>
-      <c r="V19" s="44">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="V19" s="58">
         <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="W19" s="36">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="W19" s="58">
         <f t="shared" si="4"/>
-        <v>1.4000000000000004</v>
-      </c>
-      <c r="X19" s="44">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="X19" s="58">
         <f t="shared" si="1"/>
-        <v>0.79999999999999993</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="Y19" s="32" t="s">
         <v>387</v>
       </c>
       <c r="Z19" s="48" t="s">
-        <v>412</v>
+        <v>364</v>
       </c>
     </row>
     <row r="20" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A20" s="7"/>
       <c r="B20" s="45" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>399</v>
+        <v>255</v>
       </c>
       <c r="D20" s="45">
         <v>7</v>
@@ -9736,46 +9850,60 @@
       <c r="L20" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="M20" s="45"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="36">
-        <v>0.7</v>
-      </c>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="44">
+      <c r="M20" s="45">
+        <v>0</v>
+      </c>
+      <c r="N20" s="45">
+        <v>0</v>
+      </c>
+      <c r="O20" s="58">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="P20" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="58">
         <f t="shared" si="0"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="R20" s="44"/>
-      <c r="S20" s="36">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="R20" s="58">
+        <v>0</v>
+      </c>
+      <c r="S20" s="58">
         <f t="shared" si="2"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="T20" s="44"/>
-      <c r="U20" s="44">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="T20" s="58">
+        <v>0</v>
+      </c>
+      <c r="U20" s="58">
         <f t="shared" si="3"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="V20" s="44"/>
-      <c r="W20" s="36">
+        <v>1</v>
+      </c>
+      <c r="V20" s="58">
+        <v>0</v>
+      </c>
+      <c r="W20" s="58">
         <f t="shared" si="4"/>
-        <v>1.0999999999999999</v>
-      </c>
-      <c r="X20" s="44"/>
+        <v>1.10000002384186</v>
+      </c>
+      <c r="X20" s="58">
+        <v>0</v>
+      </c>
       <c r="Y20" s="32" t="s">
         <v>388</v>
       </c>
       <c r="Z20" s="48" t="s">
-        <v>413</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A21" s="7"/>
       <c r="B21" s="45" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>399</v>
+        <v>255</v>
       </c>
       <c r="D21" s="45">
         <v>8</v>
@@ -9802,60 +9930,64 @@
         <v>2</v>
       </c>
       <c r="L21" s="45"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="36">
-        <v>0.7</v>
-      </c>
-      <c r="P21" s="36">
-        <v>0.05</v>
-      </c>
-      <c r="Q21" s="44">
+      <c r="M21" s="45">
+        <v>0</v>
+      </c>
+      <c r="N21" s="45">
+        <v>0</v>
+      </c>
+      <c r="O21" s="58">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="P21" s="58">
+        <v>0.0500000007450581</v>
+      </c>
+      <c r="Q21" s="58">
         <f t="shared" si="0"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="R21" s="44">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="R21" s="58">
         <f t="shared" si="1"/>
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="S21" s="36">
+        <v>0.150000005960464</v>
+      </c>
+      <c r="S21" s="58">
         <f t="shared" si="2"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="T21" s="44">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="T21" s="58">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
-      <c r="U21" s="44">
+      <c r="U21" s="58">
         <f t="shared" si="3"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="V21" s="44">
+        <v>1</v>
+      </c>
+      <c r="V21" s="58">
         <f t="shared" si="1"/>
-        <v>0.35</v>
-      </c>
-      <c r="W21" s="36">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="W21" s="58">
         <f t="shared" si="4"/>
-        <v>1.0999999999999999</v>
-      </c>
-      <c r="X21" s="44">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="X21" s="58">
         <f t="shared" si="1"/>
-        <v>0.44999999999999996</v>
+        <v>0.449999988079071</v>
       </c>
       <c r="Y21" s="32" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Z21" s="48" t="s">
-        <v>413</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A22" s="7"/>
       <c r="B22" s="45" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>430</v>
+        <v>257</v>
       </c>
       <c r="D22" s="45">
         <v>1</v>
@@ -9864,7 +9996,7 @@
         <v>434</v>
       </c>
       <c r="F22" s="45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G22" s="45">
         <v>0</v>
@@ -9882,44 +10014,60 @@
         <v>0</v>
       </c>
       <c r="L22" s="45"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="36">
-        <v>1</v>
-      </c>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="44">
+      <c r="M22" s="45">
+        <v>0</v>
+      </c>
+      <c r="N22" s="45">
+        <v>0</v>
+      </c>
+      <c r="O22" s="58">
+        <v>1</v>
+      </c>
+      <c r="P22" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="58">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="R22" s="44"/>
-      <c r="S22" s="36">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="R22" s="58">
+        <v>0</v>
+      </c>
+      <c r="S22" s="58">
         <f t="shared" si="2"/>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="T22" s="44"/>
-      <c r="U22" s="44">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="T22" s="58">
+        <v>0</v>
+      </c>
+      <c r="U22" s="58">
         <f t="shared" si="3"/>
-        <v>1.3000000000000003</v>
-      </c>
-      <c r="V22" s="44"/>
-      <c r="W22" s="36">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="V22" s="58">
+        <v>0</v>
+      </c>
+      <c r="W22" s="58">
         <f t="shared" si="4"/>
-        <v>1.4000000000000004</v>
-      </c>
-      <c r="X22" s="44"/>
-      <c r="Y22" s="32"/>
+        <v>1.39999997615814</v>
+      </c>
+      <c r="X22" s="58">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z22" s="48" t="s">
-        <v>431</v>
+        <v>371</v>
       </c>
     </row>
     <row r="23" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A23" s="7"/>
       <c r="B23" s="45" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>430</v>
+        <v>257</v>
       </c>
       <c r="D23" s="45">
         <v>2</v>
@@ -9946,58 +10094,64 @@
         <v>0</v>
       </c>
       <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="36">
-        <v>1</v>
-      </c>
-      <c r="P23" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="Q23" s="44">
+      <c r="M23" s="45">
+        <v>0</v>
+      </c>
+      <c r="N23" s="45">
+        <v>0</v>
+      </c>
+      <c r="O23" s="58">
+        <v>1</v>
+      </c>
+      <c r="P23" s="58">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="Q23" s="58">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="R23" s="44">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="R23" s="58">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="S23" s="36">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="S23" s="58">
         <f t="shared" si="2"/>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="T23" s="44">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="T23" s="58">
         <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="U23" s="44">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="U23" s="58">
         <f t="shared" si="3"/>
-        <v>1.3000000000000003</v>
-      </c>
-      <c r="V23" s="44">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="V23" s="58">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="W23" s="36">
+      <c r="W23" s="58">
         <f t="shared" si="4"/>
-        <v>1.4000000000000004</v>
-      </c>
-      <c r="X23" s="44">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="X23" s="58">
         <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
-      <c r="Y23" s="32"/>
+        <v>0.600000023841858</v>
+      </c>
+      <c r="Y23" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z23" s="48" t="s">
-        <v>432</v>
+        <v>366</v>
       </c>
     </row>
     <row r="24" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A24" s="7"/>
       <c r="B24" s="45" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>430</v>
+        <v>257</v>
       </c>
       <c r="D24" s="45">
         <v>3</v>
@@ -10029,57 +10183,61 @@
       <c r="M24" s="45">
         <v>0</v>
       </c>
-      <c r="N24" s="45"/>
-      <c r="O24" s="36">
-        <v>0.7</v>
-      </c>
-      <c r="P24" s="36">
-        <v>0.7</v>
-      </c>
-      <c r="Q24" s="44">
+      <c r="N24" s="45">
+        <v>0</v>
+      </c>
+      <c r="O24" s="58">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="P24" s="58">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="Q24" s="58">
         <f t="shared" si="0"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="R24" s="44">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="R24" s="58">
         <f t="shared" si="1"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="S24" s="36">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="S24" s="58">
         <f t="shared" si="2"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="T24" s="44">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="T24" s="58">
         <f t="shared" si="1"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="U24" s="44">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="U24" s="58">
         <f t="shared" si="3"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="V24" s="44">
+        <v>1</v>
+      </c>
+      <c r="V24" s="58">
         <f t="shared" si="1"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="W24" s="36">
+        <v>1</v>
+      </c>
+      <c r="W24" s="58">
         <f t="shared" si="4"/>
-        <v>1.0999999999999999</v>
-      </c>
-      <c r="X24" s="44">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="X24" s="58">
         <f t="shared" si="1"/>
-        <v>1.0999999999999999</v>
-      </c>
-      <c r="Y24" s="32"/>
+        <v>1.10000002384186</v>
+      </c>
+      <c r="Y24" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z24" s="48" t="s">
-        <v>433</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7"/>
       <c r="B25" s="45" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>430</v>
+        <v>257</v>
       </c>
       <c r="D25" s="45">
         <v>4</v>
@@ -10106,58 +10264,64 @@
         <v>0</v>
       </c>
       <c r="L25" s="45"/>
-      <c r="M25" s="45"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="36">
-        <v>1</v>
-      </c>
-      <c r="P25" s="36">
-        <v>0.1</v>
-      </c>
-      <c r="Q25" s="44">
+      <c r="M25" s="45">
+        <v>0</v>
+      </c>
+      <c r="N25" s="45">
+        <v>0</v>
+      </c>
+      <c r="O25" s="58">
+        <v>1</v>
+      </c>
+      <c r="P25" s="58">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="Q25" s="58">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="R25" s="44">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="R25" s="58">
         <f t="shared" si="1"/>
-        <v>0.2</v>
-      </c>
-      <c r="S25" s="36">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="S25" s="58">
         <f t="shared" si="2"/>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="T25" s="44">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="T25" s="58">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="U25" s="44">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="U25" s="58">
         <f t="shared" si="3"/>
-        <v>1.3000000000000003</v>
-      </c>
-      <c r="V25" s="44">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="V25" s="58">
         <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="W25" s="36">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="W25" s="58">
         <f t="shared" si="4"/>
-        <v>1.4000000000000004</v>
-      </c>
-      <c r="X25" s="44">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="X25" s="58">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="Y25" s="32"/>
+      <c r="Y25" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z25" s="48" t="s">
-        <v>431</v>
+        <v>371</v>
       </c>
     </row>
     <row r="26" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A26" s="7"/>
       <c r="B26" s="45" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>430</v>
+        <v>257</v>
       </c>
       <c r="D26" s="45">
         <v>5</v>
@@ -10166,7 +10330,7 @@
         <v>438</v>
       </c>
       <c r="F26" s="45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G26" s="45">
         <v>0</v>
@@ -10184,46 +10348,60 @@
         <v>0</v>
       </c>
       <c r="L26" s="45"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="36">
-        <v>1.2</v>
-      </c>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="44">
+      <c r="M26" s="45">
+        <v>0</v>
+      </c>
+      <c r="N26" s="45">
+        <v>0</v>
+      </c>
+      <c r="O26" s="58">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="P26" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="58">
         <f t="shared" si="0"/>
-        <v>1.3</v>
-      </c>
-      <c r="R26" s="44"/>
-      <c r="S26" s="36">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="R26" s="58">
+        <v>0</v>
+      </c>
+      <c r="S26" s="58">
         <f t="shared" si="2"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="T26" s="44"/>
-      <c r="U26" s="44">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="T26" s="58">
+        <v>0</v>
+      </c>
+      <c r="U26" s="58">
         <f t="shared" si="3"/>
-        <v>1.5000000000000002</v>
-      </c>
-      <c r="V26" s="44"/>
-      <c r="W26" s="36">
+        <v>1.5</v>
+      </c>
+      <c r="V26" s="58">
+        <v>0</v>
+      </c>
+      <c r="W26" s="58">
         <f t="shared" si="4"/>
-        <v>1.6000000000000003</v>
-      </c>
-      <c r="X26" s="44"/>
+        <v>1.60000002384186</v>
+      </c>
+      <c r="X26" s="58">
+        <v>0</v>
+      </c>
       <c r="Y26" s="32" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Z26" s="48" t="s">
-        <v>431</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A27" s="7"/>
       <c r="B27" s="45" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>430</v>
+        <v>257</v>
       </c>
       <c r="D27" s="45">
         <v>6</v>
@@ -10250,60 +10428,64 @@
         <v>0</v>
       </c>
       <c r="L27" s="45"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="36">
-        <v>1.2</v>
-      </c>
-      <c r="P27" s="36">
-        <v>0.3</v>
-      </c>
-      <c r="Q27" s="44">
+      <c r="M27" s="45">
+        <v>0</v>
+      </c>
+      <c r="N27" s="45">
+        <v>0</v>
+      </c>
+      <c r="O27" s="58">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="P27" s="58">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="Q27" s="58">
         <f t="shared" si="0"/>
-        <v>1.3</v>
-      </c>
-      <c r="R27" s="44">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="R27" s="58">
         <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="S27" s="36">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="S27" s="58">
         <f t="shared" si="2"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="T27" s="44">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="T27" s="58">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="U27" s="44">
+      <c r="U27" s="58">
         <f t="shared" si="3"/>
-        <v>1.5000000000000002</v>
-      </c>
-      <c r="V27" s="44">
+        <v>1.5</v>
+      </c>
+      <c r="V27" s="58">
         <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
-      <c r="W27" s="36">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="W27" s="58">
         <f t="shared" si="4"/>
-        <v>1.6000000000000003</v>
-      </c>
-      <c r="X27" s="44">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="X27" s="58">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.699999988079071</v>
       </c>
       <c r="Y27" s="32" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Z27" s="48" t="s">
-        <v>432</v>
+        <v>366</v>
       </c>
     </row>
     <row r="28" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A28" s="7"/>
       <c r="B28" s="45" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>430</v>
+        <v>257</v>
       </c>
       <c r="D28" s="45">
         <v>7</v>
@@ -10335,59 +10517,61 @@
       <c r="M28" s="45">
         <v>0</v>
       </c>
-      <c r="N28" s="45"/>
-      <c r="O28" s="36">
-        <v>0.9</v>
-      </c>
-      <c r="P28" s="36">
-        <v>0.9</v>
-      </c>
-      <c r="Q28" s="44">
+      <c r="N28" s="45">
+        <v>0</v>
+      </c>
+      <c r="O28" s="58">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="P28" s="58">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="Q28" s="58">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="R28" s="44">
+      <c r="R28" s="58">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S28" s="36">
+      <c r="S28" s="58">
         <f t="shared" si="2"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="T28" s="44">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="T28" s="58">
         <f t="shared" si="1"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="U28" s="44">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="U28" s="58">
         <f t="shared" si="3"/>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="V28" s="44">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="V28" s="58">
         <f t="shared" si="1"/>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="W28" s="36">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="W28" s="58">
         <f t="shared" si="4"/>
-        <v>1.3000000000000003</v>
-      </c>
-      <c r="X28" s="44">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="X28" s="58">
         <f t="shared" si="1"/>
-        <v>1.3000000000000003</v>
+        <v>1.29999995231628</v>
       </c>
       <c r="Y28" s="32" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Z28" s="48" t="s">
-        <v>433</v>
+        <v>369</v>
       </c>
     </row>
     <row r="29" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A29" s="7"/>
       <c r="B29" s="45" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>430</v>
+        <v>257</v>
       </c>
       <c r="D29" s="45">
         <v>8</v>
@@ -10414,60 +10598,64 @@
         <v>0</v>
       </c>
       <c r="L29" s="45"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="36">
-        <v>1.2</v>
-      </c>
-      <c r="P29" s="36">
-        <v>0.15</v>
-      </c>
-      <c r="Q29" s="44">
+      <c r="M29" s="45">
+        <v>0</v>
+      </c>
+      <c r="N29" s="45">
+        <v>0</v>
+      </c>
+      <c r="O29" s="58">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="P29" s="58">
+        <v>0.150000005960464</v>
+      </c>
+      <c r="Q29" s="58">
         <f t="shared" si="0"/>
-        <v>1.3</v>
-      </c>
-      <c r="R29" s="44">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="R29" s="58">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
-      <c r="S29" s="36">
+      <c r="S29" s="58">
         <f t="shared" si="2"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="T29" s="44">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="T29" s="58">
         <f t="shared" si="1"/>
-        <v>0.35</v>
-      </c>
-      <c r="U29" s="44">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="U29" s="58">
         <f t="shared" si="3"/>
-        <v>1.5000000000000002</v>
-      </c>
-      <c r="V29" s="44">
+        <v>1.5</v>
+      </c>
+      <c r="V29" s="58">
         <f t="shared" si="1"/>
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="W29" s="36">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="W29" s="58">
         <f t="shared" si="4"/>
-        <v>1.6000000000000003</v>
-      </c>
-      <c r="X29" s="44">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="X29" s="58">
         <f t="shared" si="1"/>
-        <v>0.54999999999999993</v>
+        <v>0.550000011920929</v>
       </c>
       <c r="Y29" s="32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Z29" s="48" t="s">
-        <v>431</v>
+        <v>371</v>
       </c>
     </row>
     <row r="30" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A30" s="7"/>
       <c r="B30" s="45" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>463</v>
+        <v>259</v>
       </c>
       <c r="D30" s="45">
         <v>1</v>
@@ -10494,44 +10682,60 @@
         <v>0</v>
       </c>
       <c r="L30" s="45"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="36">
+      <c r="M30" s="45">
+        <v>0</v>
+      </c>
+      <c r="N30" s="45">
+        <v>0</v>
+      </c>
+      <c r="O30" s="58">
         <v>0.5</v>
       </c>
-      <c r="P30" s="36"/>
-      <c r="Q30" s="44">
+      <c r="P30" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="58">
         <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-      <c r="R30" s="44"/>
-      <c r="S30" s="36">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="R30" s="58">
+        <v>0</v>
+      </c>
+      <c r="S30" s="58">
         <f t="shared" si="2"/>
-        <v>0.7</v>
-      </c>
-      <c r="T30" s="44"/>
-      <c r="U30" s="44">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="T30" s="58">
+        <v>0</v>
+      </c>
+      <c r="U30" s="58">
         <f t="shared" si="3"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="V30" s="44"/>
-      <c r="W30" s="36">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="V30" s="58">
+        <v>0</v>
+      </c>
+      <c r="W30" s="58">
         <f t="shared" si="4"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="X30" s="44"/>
-      <c r="Y30" s="32"/>
+        <v>0.899999976158142</v>
+      </c>
+      <c r="X30" s="58">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z30" s="48" t="s">
-        <v>460</v>
+        <v>376</v>
       </c>
     </row>
     <row r="31" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A31" s="7"/>
       <c r="B31" s="45" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>463</v>
+        <v>259</v>
       </c>
       <c r="D31" s="45">
         <v>2</v>
@@ -10558,44 +10762,60 @@
         <v>0</v>
       </c>
       <c r="L31" s="45"/>
-      <c r="M31" s="45"/>
-      <c r="N31" s="45"/>
-      <c r="O31" s="36">
-        <v>0.8</v>
-      </c>
-      <c r="P31" s="36"/>
-      <c r="Q31" s="44">
+      <c r="M31" s="45">
+        <v>0</v>
+      </c>
+      <c r="N31" s="45">
+        <v>0</v>
+      </c>
+      <c r="O31" s="58">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="P31" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="58">
         <f t="shared" si="0"/>
-        <v>0.9</v>
-      </c>
-      <c r="R31" s="44"/>
-      <c r="S31" s="36">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="R31" s="58">
+        <v>0</v>
+      </c>
+      <c r="S31" s="58">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="T31" s="44"/>
-      <c r="U31" s="44">
+      <c r="T31" s="58">
+        <v>0</v>
+      </c>
+      <c r="U31" s="58">
         <f t="shared" si="3"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="V31" s="44"/>
-      <c r="W31" s="36">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="V31" s="58">
+        <v>0</v>
+      </c>
+      <c r="W31" s="58">
         <f t="shared" si="4"/>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="X31" s="44"/>
-      <c r="Y31" s="32"/>
+        <v>1.20000004768372</v>
+      </c>
+      <c r="X31" s="58">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z31" s="48" t="s">
-        <v>461</v>
+        <v>380</v>
       </c>
     </row>
     <row r="32" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A32" s="7"/>
       <c r="B32" s="45" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>463</v>
+        <v>259</v>
       </c>
       <c r="D32" s="45">
         <v>3</v>
@@ -10630,56 +10850,58 @@
       <c r="N32" s="45">
         <v>1</v>
       </c>
-      <c r="O32" s="36">
-        <v>0.3</v>
-      </c>
-      <c r="P32" s="36">
-        <v>0.3</v>
-      </c>
-      <c r="Q32" s="44">
+      <c r="O32" s="58">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="P32" s="58">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="Q32" s="58">
         <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="R32" s="44">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="R32" s="58">
         <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="S32" s="36">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="S32" s="58">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="T32" s="44">
+      <c r="T32" s="58">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="U32" s="44">
+      <c r="U32" s="58">
         <f t="shared" si="3"/>
-        <v>0.6</v>
-      </c>
-      <c r="V32" s="44">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="V32" s="58">
         <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
-      <c r="W32" s="36">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="W32" s="58">
         <f t="shared" si="4"/>
-        <v>0.7</v>
-      </c>
-      <c r="X32" s="44">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="X32" s="58">
         <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="Y32" s="32"/>
+        <v>0.699999988079071</v>
+      </c>
+      <c r="Y32" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z32" s="48" t="s">
-        <v>462</v>
+        <v>378</v>
       </c>
     </row>
     <row r="33" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A33" s="7"/>
       <c r="B33" s="45" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>463</v>
+        <v>259</v>
       </c>
       <c r="D33" s="45">
         <v>4</v>
@@ -10706,58 +10928,64 @@
         <v>2</v>
       </c>
       <c r="L33" s="45"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="P33" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="Q33" s="44">
+      <c r="M33" s="45">
+        <v>0</v>
+      </c>
+      <c r="N33" s="45">
+        <v>0</v>
+      </c>
+      <c r="O33" s="58">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="P33" s="58">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="Q33" s="58">
         <f t="shared" si="0"/>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="R33" s="44">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="R33" s="58">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="S33" s="36">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="S33" s="58">
         <f t="shared" si="2"/>
-        <v>0.4</v>
-      </c>
-      <c r="T33" s="44">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="T33" s="58">
         <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="U33" s="44">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="U33" s="58">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="V33" s="44">
+      <c r="V33" s="58">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="W33" s="36">
+      <c r="W33" s="58">
         <f t="shared" si="4"/>
-        <v>0.6</v>
-      </c>
-      <c r="X33" s="44">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="X33" s="58">
         <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
-      <c r="Y33" s="32"/>
+        <v>0.600000023841858</v>
+      </c>
+      <c r="Y33" s="32" t="s">
+        <v>531</v>
+      </c>
       <c r="Z33" s="48" t="s">
-        <v>460</v>
+        <v>376</v>
       </c>
     </row>
     <row r="34" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A34" s="7"/>
       <c r="B34" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C34" s="45" t="s">
-        <v>463</v>
+        <v>259</v>
       </c>
       <c r="D34" s="45">
         <v>5</v>
@@ -10784,46 +11012,60 @@
         <v>0</v>
       </c>
       <c r="L34" s="45"/>
-      <c r="M34" s="45"/>
-      <c r="N34" s="45"/>
-      <c r="O34" s="36">
-        <v>0.7</v>
-      </c>
-      <c r="P34" s="36"/>
-      <c r="Q34" s="44">
+      <c r="M34" s="45">
+        <v>0</v>
+      </c>
+      <c r="N34" s="45">
+        <v>0</v>
+      </c>
+      <c r="O34" s="58">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="P34" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="58">
         <f t="shared" si="0"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="R34" s="44"/>
-      <c r="S34" s="36">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="R34" s="58">
+        <v>0</v>
+      </c>
+      <c r="S34" s="58">
         <f t="shared" si="2"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="T34" s="44"/>
-      <c r="U34" s="44">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="T34" s="58">
+        <v>0</v>
+      </c>
+      <c r="U34" s="58">
         <f t="shared" si="3"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="V34" s="44"/>
-      <c r="W34" s="36">
+        <v>1</v>
+      </c>
+      <c r="V34" s="58">
+        <v>0</v>
+      </c>
+      <c r="W34" s="58">
         <f t="shared" si="4"/>
-        <v>1.0999999999999999</v>
-      </c>
-      <c r="X34" s="44"/>
+        <v>1.10000002384186</v>
+      </c>
+      <c r="X34" s="58">
+        <v>0</v>
+      </c>
       <c r="Y34" s="32" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Z34" s="48" t="s">
-        <v>460</v>
+        <v>376</v>
       </c>
     </row>
     <row r="35" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A35" s="7"/>
       <c r="B35" s="45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>463</v>
+        <v>259</v>
       </c>
       <c r="D35" s="45">
         <v>6</v>
@@ -10850,46 +11092,60 @@
         <v>0</v>
       </c>
       <c r="L35" s="45"/>
-      <c r="M35" s="45"/>
-      <c r="N35" s="45"/>
-      <c r="O35" s="36">
-        <v>1</v>
-      </c>
-      <c r="P35" s="36"/>
-      <c r="Q35" s="44">
+      <c r="M35" s="45">
+        <v>0</v>
+      </c>
+      <c r="N35" s="45">
+        <v>0</v>
+      </c>
+      <c r="O35" s="58">
+        <v>1</v>
+      </c>
+      <c r="P35" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="58">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="R35" s="44"/>
-      <c r="S35" s="36">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="R35" s="58">
+        <v>0</v>
+      </c>
+      <c r="S35" s="58">
         <f t="shared" si="2"/>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="T35" s="44"/>
-      <c r="U35" s="44">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="T35" s="58">
+        <v>0</v>
+      </c>
+      <c r="U35" s="58">
         <f t="shared" si="3"/>
-        <v>1.3000000000000003</v>
-      </c>
-      <c r="V35" s="44"/>
-      <c r="W35" s="36">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="V35" s="58">
+        <v>0</v>
+      </c>
+      <c r="W35" s="58">
         <f t="shared" si="4"/>
-        <v>1.4000000000000004</v>
-      </c>
-      <c r="X35" s="44"/>
+        <v>1.39999997615814</v>
+      </c>
+      <c r="X35" s="58">
+        <v>0</v>
+      </c>
       <c r="Y35" s="32" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z35" s="48" t="s">
-        <v>461</v>
+        <v>380</v>
       </c>
     </row>
     <row r="36" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A36" s="7"/>
       <c r="B36" s="45" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C36" s="45" t="s">
-        <v>463</v>
+        <v>259</v>
       </c>
       <c r="D36" s="45">
         <v>7</v>
@@ -10924,58 +11180,58 @@
       <c r="N36" s="45">
         <v>1</v>
       </c>
-      <c r="O36" s="36">
+      <c r="O36" s="58">
         <v>0.5</v>
       </c>
-      <c r="P36" s="36">
+      <c r="P36" s="58">
         <v>0.5</v>
       </c>
-      <c r="Q36" s="44">
+      <c r="Q36" s="58">
         <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-      <c r="R36" s="44">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="R36" s="58">
         <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
-      <c r="S36" s="36">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="S36" s="58">
         <f t="shared" si="2"/>
-        <v>0.7</v>
-      </c>
-      <c r="T36" s="44">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="T36" s="58">
         <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="U36" s="44">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="U36" s="58">
         <f t="shared" si="3"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="V36" s="44">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="V36" s="58">
         <f t="shared" si="1"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="W36" s="36">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="W36" s="58">
         <f t="shared" si="4"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="X36" s="44">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="X36" s="58">
         <f t="shared" si="1"/>
-        <v>0.89999999999999991</v>
+        <v>0.899999976158142</v>
       </c>
       <c r="Y36" s="32" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z36" s="48" t="s">
-        <v>462</v>
+        <v>378</v>
       </c>
     </row>
     <row r="37" spans="1:26" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A37" s="7"/>
       <c r="B37" s="45" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C37" s="45" t="s">
-        <v>463</v>
+        <v>259</v>
       </c>
       <c r="D37" s="45">
         <v>8</v>
@@ -11002,51 +11258,55 @@
         <v>2</v>
       </c>
       <c r="L37" s="45"/>
-      <c r="M37" s="45"/>
-      <c r="N37" s="45"/>
-      <c r="O37" s="36">
-        <v>0.3</v>
-      </c>
-      <c r="P37" s="36">
-        <v>0.3</v>
-      </c>
-      <c r="Q37" s="44">
+      <c r="M37" s="45">
+        <v>0</v>
+      </c>
+      <c r="N37" s="45">
+        <v>0</v>
+      </c>
+      <c r="O37" s="58">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="P37" s="58">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="Q37" s="58">
         <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="R37" s="44">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="R37" s="58">
         <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="S37" s="36">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="S37" s="58">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="T37" s="44">
+      <c r="T37" s="58">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="U37" s="44">
+      <c r="U37" s="58">
         <f t="shared" si="3"/>
-        <v>0.6</v>
-      </c>
-      <c r="V37" s="44">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="V37" s="58">
         <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
-      <c r="W37" s="36">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="W37" s="58">
         <f t="shared" si="4"/>
-        <v>0.7</v>
-      </c>
-      <c r="X37" s="44">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="X37" s="58">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.699999988079071</v>
       </c>
       <c r="Y37" s="32" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Z37" s="48" t="s">
-        <v>460</v>
+        <v>376</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.45">
